--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SDGIO:00010029</t>
+          <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SDGIO:00010028</t>
+          <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q388" t="inlineStr"/>
@@ -18411,7 +18411,7 @@
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q389" t="inlineStr"/>
@@ -18462,7 +18462,7 @@
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q390" t="inlineStr"/>
@@ -31569,7 +31569,7 @@
       <c r="O647" t="inlineStr"/>
       <c r="P647" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q647" t="inlineStr"/>
@@ -31620,7 +31620,7 @@
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q648" t="inlineStr"/>
@@ -31671,7 +31671,7 @@
       <c r="O649" t="inlineStr"/>
       <c r="P649" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q649" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q388" t="inlineStr"/>
@@ -18411,7 +18411,7 @@
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q389" t="inlineStr"/>
@@ -18462,7 +18462,7 @@
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q390" t="inlineStr"/>
@@ -31569,7 +31569,7 @@
       <c r="O647" t="inlineStr"/>
       <c r="P647" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q647" t="inlineStr"/>
@@ -31620,7 +31620,7 @@
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q648" t="inlineStr"/>
@@ -31671,7 +31671,7 @@
       <c r="O649" t="inlineStr"/>
       <c r="P649" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="Q649" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18096,7 @@
       <c r="Q384" t="inlineStr"/>
       <c r="R384" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S384" t="inlineStr"/>
@@ -18147,7 +18147,7 @@
       <c r="Q385" t="inlineStr"/>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S385" t="inlineStr"/>
@@ -18198,7 +18198,7 @@
       <c r="Q386" t="inlineStr"/>
       <c r="R386" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S386" t="inlineStr"/>
@@ -21615,7 +21615,7 @@
       <c r="Q453" t="inlineStr"/>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S453" t="inlineStr"/>
@@ -21666,7 +21666,7 @@
       <c r="Q454" t="inlineStr"/>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S454" t="inlineStr"/>
@@ -21717,7 +21717,7 @@
       <c r="Q455" t="inlineStr"/>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S455" t="inlineStr"/>
@@ -22992,7 +22992,7 @@
       <c r="Q480" t="inlineStr"/>
       <c r="R480" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S480" t="inlineStr"/>
@@ -23043,7 +23043,7 @@
       <c r="Q481" t="inlineStr"/>
       <c r="R481" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S481" t="inlineStr"/>
@@ -23094,7 +23094,7 @@
       <c r="Q482" t="inlineStr"/>
       <c r="R482" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S482" t="inlineStr"/>
@@ -26919,7 +26919,7 @@
       <c r="Q557" t="inlineStr"/>
       <c r="R557" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S557" t="inlineStr"/>
@@ -26970,7 +26970,7 @@
       <c r="Q558" t="inlineStr"/>
       <c r="R558" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S558" t="inlineStr"/>
@@ -27021,7 +27021,7 @@
       <c r="Q559" t="inlineStr"/>
       <c r="R559" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S559" t="inlineStr"/>
@@ -29010,7 +29010,7 @@
       <c r="Q598" t="inlineStr"/>
       <c r="R598" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S598" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
       <c r="Q599" t="inlineStr"/>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S599" t="inlineStr"/>
@@ -29112,7 +29112,7 @@
       <c r="Q600" t="inlineStr"/>
       <c r="R600" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S600" t="inlineStr"/>
@@ -39771,7 +39771,7 @@
       <c r="Q809" t="inlineStr"/>
       <c r="R809" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S809" t="inlineStr"/>
@@ -39822,7 +39822,7 @@
       <c r="Q810" t="inlineStr"/>
       <c r="R810" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S810" t="inlineStr"/>
@@ -39873,7 +39873,7 @@
       <c r="Q811" t="inlineStr"/>
       <c r="R811" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S811" t="inlineStr"/>
@@ -43851,7 +43851,7 @@
       <c r="Q889" t="inlineStr"/>
       <c r="R889" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S889" t="inlineStr"/>
@@ -43902,7 +43902,7 @@
       <c r="Q890" t="inlineStr"/>
       <c r="R890" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S890" t="inlineStr"/>
@@ -43953,7 +43953,7 @@
       <c r="Q891" t="inlineStr"/>
       <c r="R891" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S891" t="inlineStr"/>
@@ -44718,7 +44718,7 @@
       <c r="Q906" t="inlineStr"/>
       <c r="R906" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S906" t="inlineStr"/>
@@ -44769,7 +44769,7 @@
       <c r="Q907" t="inlineStr"/>
       <c r="R907" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S907" t="inlineStr"/>
@@ -44820,7 +44820,7 @@
       <c r="Q908" t="inlineStr"/>
       <c r="R908" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S908" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18096,7 @@
       <c r="Q384" t="inlineStr"/>
       <c r="R384" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S384" t="inlineStr"/>
@@ -18147,7 +18147,7 @@
       <c r="Q385" t="inlineStr"/>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S385" t="inlineStr"/>
@@ -18198,7 +18198,7 @@
       <c r="Q386" t="inlineStr"/>
       <c r="R386" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S386" t="inlineStr"/>
@@ -21615,7 +21615,7 @@
       <c r="Q453" t="inlineStr"/>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S453" t="inlineStr"/>
@@ -21666,7 +21666,7 @@
       <c r="Q454" t="inlineStr"/>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S454" t="inlineStr"/>
@@ -21717,7 +21717,7 @@
       <c r="Q455" t="inlineStr"/>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S455" t="inlineStr"/>
@@ -22992,7 +22992,7 @@
       <c r="Q480" t="inlineStr"/>
       <c r="R480" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S480" t="inlineStr"/>
@@ -23043,7 +23043,7 @@
       <c r="Q481" t="inlineStr"/>
       <c r="R481" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S481" t="inlineStr"/>
@@ -23094,7 +23094,7 @@
       <c r="Q482" t="inlineStr"/>
       <c r="R482" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S482" t="inlineStr"/>
@@ -26919,7 +26919,7 @@
       <c r="Q557" t="inlineStr"/>
       <c r="R557" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S557" t="inlineStr"/>
@@ -26970,7 +26970,7 @@
       <c r="Q558" t="inlineStr"/>
       <c r="R558" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S558" t="inlineStr"/>
@@ -27021,7 +27021,7 @@
       <c r="Q559" t="inlineStr"/>
       <c r="R559" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S559" t="inlineStr"/>
@@ -29010,7 +29010,7 @@
       <c r="Q598" t="inlineStr"/>
       <c r="R598" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S598" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
       <c r="Q599" t="inlineStr"/>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S599" t="inlineStr"/>
@@ -29112,7 +29112,7 @@
       <c r="Q600" t="inlineStr"/>
       <c r="R600" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S600" t="inlineStr"/>
@@ -39771,7 +39771,7 @@
       <c r="Q809" t="inlineStr"/>
       <c r="R809" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S809" t="inlineStr"/>
@@ -39822,7 +39822,7 @@
       <c r="Q810" t="inlineStr"/>
       <c r="R810" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S810" t="inlineStr"/>
@@ -39873,7 +39873,7 @@
       <c r="Q811" t="inlineStr"/>
       <c r="R811" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S811" t="inlineStr"/>
@@ -43851,7 +43851,7 @@
       <c r="Q889" t="inlineStr"/>
       <c r="R889" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S889" t="inlineStr"/>
@@ -43902,7 +43902,7 @@
       <c r="Q890" t="inlineStr"/>
       <c r="R890" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S890" t="inlineStr"/>
@@ -43953,7 +43953,7 @@
       <c r="Q891" t="inlineStr"/>
       <c r="R891" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S891" t="inlineStr"/>
@@ -44718,7 +44718,7 @@
       <c r="Q906" t="inlineStr"/>
       <c r="R906" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S906" t="inlineStr"/>
@@ -44769,7 +44769,7 @@
       <c r="Q907" t="inlineStr"/>
       <c r="R907" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S907" t="inlineStr"/>
@@ -44820,7 +44820,7 @@
       <c r="Q908" t="inlineStr"/>
       <c r="R908" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S908" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U954"/>
+  <dimension ref="A1:U930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14621,7 +14621,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BCIO:015231</t>
+          <t>BCIO:015808</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14672,7 +14672,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BCIO:015232</t>
+          <t>BCIO:015809</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14723,7 +14723,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BCIO:015233</t>
+          <t>BCIO:015810</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>BCIO:015234</t>
+          <t>BCIO:015811</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14825,7 +14825,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>BCIO:015235</t>
+          <t>BCIO:015812</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14876,7 +14876,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>BCIO:015236</t>
+          <t>BCIO:015813</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14927,7 +14927,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BCIO:015237</t>
+          <t>BCIO:015814</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14978,7 +14978,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BCIO:015846</t>
+          <t>BCIO:015815</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -15029,7 +15029,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BCIO:015847</t>
+          <t>BCIO:015816</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -15080,7 +15080,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BCIO:015848</t>
+          <t>BCIO:015817</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -15131,7 +15131,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BCIO:015849</t>
+          <t>BCIO:015818</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -15182,7 +15182,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>BCIO:015850</t>
+          <t>BCIO:015819</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -15233,7 +15233,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BCIO:015851</t>
+          <t>BCIO:015820</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -15284,7 +15284,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>BCIO:015852</t>
+          <t>BCIO:015821</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -15335,7 +15335,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>BCIO:015238</t>
+          <t>BCIO:015231</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -15386,7 +15386,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>BCIO:015239</t>
+          <t>BCIO:015232</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -15437,7 +15437,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>BCIO:015240</t>
+          <t>BCIO:015233</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BCIO:015241</t>
+          <t>BCIO:015234</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -15539,7 +15539,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BCIO:015242</t>
+          <t>BCIO:015235</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -15590,7 +15590,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BCIO:015243</t>
+          <t>BCIO:015236</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -15641,7 +15641,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BCIO:015244</t>
+          <t>BCIO:015237</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -15692,7 +15692,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BCIO:015245</t>
+          <t>BCIO:015238</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -15743,7 +15743,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BCIO:015246</t>
+          <t>BCIO:015239</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -15794,7 +15794,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>BCIO:015247</t>
+          <t>BCIO:015240</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -15845,7 +15845,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BCIO:015248</t>
+          <t>BCIO:015241</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -15896,7 +15896,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BCIO:015249</t>
+          <t>BCIO:015242</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -15947,7 +15947,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BCIO:015250</t>
+          <t>BCIO:015243</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -15998,7 +15998,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BCIO:015251</t>
+          <t>BCIO:015244</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -16049,7 +16049,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BCIO:015252</t>
+          <t>BCIO:015245</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -16100,7 +16100,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>BCIO:015253</t>
+          <t>BCIO:015246</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -16151,7 +16151,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BCIO:015254</t>
+          <t>BCIO:015247</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BCIO:015255</t>
+          <t>BCIO:015248</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -16253,7 +16253,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BCIO:015256</t>
+          <t>BCIO:015249</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -16304,7 +16304,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BCIO:015257</t>
+          <t>BCIO:015250</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -16355,7 +16355,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BCIO:015258</t>
+          <t>BCIO:015251</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BCIO:015259</t>
+          <t>BCIO:015252</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -16457,7 +16457,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>BCIO:015260</t>
+          <t>BCIO:015253</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -16508,7 +16508,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BCIO:015261</t>
+          <t>BCIO:015254</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -16559,7 +16559,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BCIO:015262</t>
+          <t>BCIO:015255</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -16610,7 +16610,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BCIO:015263</t>
+          <t>BCIO:015256</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -16661,7 +16661,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>BCIO:015264</t>
+          <t>BCIO:015257</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -16712,7 +16712,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BCIO:015265</t>
+          <t>BCIO:015258</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -16763,7 +16763,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>BCIO:015266</t>
+          <t>BCIO:015259</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>BCIO:015267</t>
+          <t>BCIO:015260</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -16865,7 +16865,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BCIO:015268</t>
+          <t>BCIO:015261</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>BCIO:015269</t>
+          <t>BCIO:015262</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16967,7 +16967,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>BCIO:015270</t>
+          <t>BCIO:015263</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -17018,7 +17018,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>BCIO:015271</t>
+          <t>BCIO:015264</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -17069,7 +17069,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>BCIO:015272</t>
+          <t>BCIO:015265</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -17120,7 +17120,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>BCIO:015273</t>
+          <t>BCIO:015266</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -17171,7 +17171,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>BCIO:015274</t>
+          <t>BCIO:015267</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -17222,7 +17222,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>BCIO:015275</t>
+          <t>BCIO:015268</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -17273,7 +17273,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>BCIO:015276</t>
+          <t>BCIO:015269</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -17324,7 +17324,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>BCIO:015277</t>
+          <t>BCIO:015270</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>BCIO:015278</t>
+          <t>BCIO:015271</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -17426,7 +17426,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>BCIO:015279</t>
+          <t>BCIO:015272</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -17477,7 +17477,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>BCIO:015280</t>
+          <t>BCIO:015273</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -17528,7 +17528,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>BCIO:015281</t>
+          <t>BCIO:015274</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -17579,7 +17579,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>BCIO:015282</t>
+          <t>BCIO:015275</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>BCIO:015283</t>
+          <t>BCIO:015276</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -17681,7 +17681,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>BCIO:015284</t>
+          <t>BCIO:015277</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -17732,7 +17732,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>BCIO:015285</t>
+          <t>BCIO:015278</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -17783,7 +17783,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>BCIO:015286</t>
+          <t>BCIO:015279</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -17834,7 +17834,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BCIO:015287</t>
+          <t>BCIO:015280</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -17885,7 +17885,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>BCIO:015288</t>
+          <t>BCIO:015281</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -17936,7 +17936,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>BCIO:015289</t>
+          <t>BCIO:015282</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -17987,7 +17987,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>BCIO:015290</t>
+          <t>BCIO:015283</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -18038,7 +18038,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>BCIO:015291</t>
+          <t>BCIO:015284</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -18089,7 +18089,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BCIO:015292</t>
+          <t>BCIO:015285</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -18140,7 +18140,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>BCIO:015293</t>
+          <t>BCIO:015286</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -18191,7 +18191,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>BCIO:015294</t>
+          <t>BCIO:015287</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -18242,7 +18242,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>BCIO:015295</t>
+          <t>BCIO:015288</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -18293,7 +18293,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>BCIO:015296</t>
+          <t>BCIO:015289</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>BCIO:015297</t>
+          <t>BCIO:015290</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -18395,7 +18395,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>BCIO:015298</t>
+          <t>BCIO:015291</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -18446,7 +18446,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>BCIO:015299</t>
+          <t>BCIO:015292</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -18497,7 +18497,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>BCIO:015300</t>
+          <t>BCIO:015293</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -18548,7 +18548,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>BCIO:015301</t>
+          <t>BCIO:015294</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -18599,7 +18599,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BCIO:015302</t>
+          <t>BCIO:015295</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -18650,7 +18650,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>BCIO:015303</t>
+          <t>BCIO:015296</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -18701,7 +18701,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>BCIO:015307</t>
+          <t>BCIO:015297</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -18752,7 +18752,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>BCIO:015308</t>
+          <t>BCIO:015298</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -18803,7 +18803,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>BCIO:015309</t>
+          <t>BCIO:015299</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -18854,7 +18854,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>BCIO:015310</t>
+          <t>BCIO:015300</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -18905,7 +18905,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>BCIO:015311</t>
+          <t>BCIO:015301</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -18956,7 +18956,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>BCIO:015312</t>
+          <t>BCIO:015302</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -19007,7 +19007,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>BCIO:015313</t>
+          <t>BCIO:015303</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>BCIO:015314</t>
+          <t>BCIO:015304</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -19109,7 +19109,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>BCIO:015315</t>
+          <t>BCIO:015305</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -19160,7 +19160,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>BCIO:015316</t>
+          <t>BCIO:015306</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -19211,7 +19211,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>BCIO:015317</t>
+          <t>BCIO:015307</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -19262,7 +19262,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>BCIO:015318</t>
+          <t>BCIO:015308</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -19313,7 +19313,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>BCIO:015319</t>
+          <t>BCIO:015309</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -19364,7 +19364,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>BCIO:015320</t>
+          <t>BCIO:015310</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -19415,7 +19415,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>BCIO:015321</t>
+          <t>BCIO:015311</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -19466,7 +19466,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>BCIO:015322</t>
+          <t>BCIO:015312</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -19517,7 +19517,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>BCIO:015323</t>
+          <t>BCIO:015313</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -19568,7 +19568,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>BCIO:015324</t>
+          <t>BCIO:015314</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -19619,7 +19619,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>BCIO:015325</t>
+          <t>BCIO:015315</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -19670,7 +19670,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BCIO:015326</t>
+          <t>BCIO:015316</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -19721,7 +19721,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>BCIO:015327</t>
+          <t>BCIO:015317</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>BCIO:015328</t>
+          <t>BCIO:015318</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -19823,7 +19823,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>BCIO:015329</t>
+          <t>BCIO:015319</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -19874,7 +19874,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>BCIO:015330</t>
+          <t>BCIO:015320</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -19925,7 +19925,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>BCIO:015331</t>
+          <t>BCIO:015822</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -19976,7 +19976,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>BCIO:015332</t>
+          <t>BCIO:015823</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -20027,7 +20027,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>BCIO:015333</t>
+          <t>BCIO:015824</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -20078,7 +20078,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>BCIO:015334</t>
+          <t>BCIO:015825</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -20129,7 +20129,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>BCIO:015335</t>
+          <t>BCIO:015826</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -20180,7 +20180,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BCIO:015336</t>
+          <t>BCIO:015827</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -20231,7 +20231,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>BCIO:015337</t>
+          <t>BCIO:015828</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -20282,7 +20282,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>BCIO:015338</t>
+          <t>BCIO:015321</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -20333,7 +20333,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>BCIO:015339</t>
+          <t>BCIO:015322</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -20384,7 +20384,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>BCIO:015340</t>
+          <t>BCIO:015323</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -20435,7 +20435,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>BCIO:015341</t>
+          <t>BCIO:015324</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>BCIO:015342</t>
+          <t>BCIO:015325</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -20537,7 +20537,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BCIO:015343</t>
+          <t>BCIO:015326</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -20588,7 +20588,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>BCIO:015344</t>
+          <t>BCIO:015327</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -20639,7 +20639,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>BCIO:015345</t>
+          <t>BCIO:015328</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -20690,7 +20690,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>BCIO:015346</t>
+          <t>BCIO:015329</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -20741,7 +20741,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>BCIO:015347</t>
+          <t>BCIO:015330</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -20792,7 +20792,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>BCIO:015348</t>
+          <t>BCIO:015331</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -20843,7 +20843,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>BCIO:015349</t>
+          <t>BCIO:015332</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -20894,7 +20894,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>BCIO:015350</t>
+          <t>BCIO:015333</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -20945,7 +20945,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>BCIO:015351</t>
+          <t>BCIO:015334</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -20996,7 +20996,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BCIO:015352</t>
+          <t>BCIO:015335</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -21047,7 +21047,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>BCIO:015353</t>
+          <t>BCIO:015336</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -21098,7 +21098,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>BCIO:015354</t>
+          <t>BCIO:015337</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -21149,7 +21149,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>BCIO:015355</t>
+          <t>BCIO:015338</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>BCIO:015356</t>
+          <t>BCIO:015339</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -21251,7 +21251,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>BCIO:015357</t>
+          <t>BCIO:015340</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -21302,7 +21302,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>BCIO:015358</t>
+          <t>BCIO:015341</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -21353,7 +21353,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>BCIO:015359</t>
+          <t>BCIO:015342</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -21404,7 +21404,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BCIO:015360</t>
+          <t>BCIO:015343</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -21455,7 +21455,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>BCIO:015361</t>
+          <t>BCIO:015344</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -21506,7 +21506,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>BCIO:015362</t>
+          <t>BCIO:015345</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -21557,7 +21557,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>BCIO:015363</t>
+          <t>BCIO:015346</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -21608,7 +21608,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>BCIO:015364</t>
+          <t>BCIO:015347</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -21659,7 +21659,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BCIO:015365</t>
+          <t>BCIO:015348</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -21710,7 +21710,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>BCIO:015366</t>
+          <t>BCIO:015349</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -21761,7 +21761,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>BCIO:015367</t>
+          <t>BCIO:015350</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -21812,7 +21812,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BCIO:015368</t>
+          <t>BCIO:015351</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -21863,7 +21863,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BCIO:015369</t>
+          <t>BCIO:015352</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>BCIO:015370</t>
+          <t>BCIO:015353</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -21965,7 +21965,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BCIO:015371</t>
+          <t>BCIO:015354</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -22016,7 +22016,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>BCIO:015372</t>
+          <t>BCIO:015355</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -22067,7 +22067,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BCIO:015373</t>
+          <t>BCIO:015356</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -22118,7 +22118,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BCIO:015374</t>
+          <t>BCIO:015357</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -22169,7 +22169,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BCIO:015375</t>
+          <t>BCIO:015358</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -22220,7 +22220,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BCIO:015376</t>
+          <t>BCIO:015359</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -22271,7 +22271,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>BCIO:015853</t>
+          <t>BCIO:015829</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -22322,7 +22322,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>BCIO:015854</t>
+          <t>BCIO:015830</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>BCIO:015855</t>
+          <t>BCIO:015831</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -22424,7 +22424,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>BCIO:015856</t>
+          <t>BCIO:015832</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -22475,7 +22475,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BCIO:015857</t>
+          <t>BCIO:015833</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -22526,7 +22526,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BCIO:015858</t>
+          <t>BCIO:015834</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -22577,7 +22577,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BCIO:015859</t>
+          <t>BCIO:015835</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BCIO:015377</t>
+          <t>BCIO:015360</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -22679,7 +22679,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BCIO:015378</t>
+          <t>BCIO:015361</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -22730,7 +22730,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BCIO:015379</t>
+          <t>BCIO:015362</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -22781,7 +22781,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>BCIO:015383</t>
+          <t>BCIO:015363</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -22832,7 +22832,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>BCIO:015384</t>
+          <t>BCIO:015364</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -22883,7 +22883,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>BCIO:015385</t>
+          <t>BCIO:015365</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -22934,7 +22934,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>BCIO:015386</t>
+          <t>BCIO:015366</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -22985,7 +22985,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BCIO:015387</t>
+          <t>BCIO:015367</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -23036,7 +23036,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>BCIO:015388</t>
+          <t>BCIO:015368</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -23087,7 +23087,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>BCIO:015389</t>
+          <t>BCIO:015369</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -23138,7 +23138,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BCIO:015390</t>
+          <t>BCIO:015370</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -23189,7 +23189,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BCIO:015391</t>
+          <t>BCIO:015371</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -23240,7 +23240,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BCIO:015392</t>
+          <t>BCIO:015372</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -23291,7 +23291,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BCIO:015393</t>
+          <t>BCIO:015373</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BCIO:015394</t>
+          <t>BCIO:015374</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -23393,7 +23393,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BCIO:015395</t>
+          <t>BCIO:015375</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -23444,7 +23444,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BCIO:015396</t>
+          <t>BCIO:015376</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -23495,7 +23495,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BCIO:015397</t>
+          <t>BCIO:015377</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -23546,7 +23546,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>BCIO:015398</t>
+          <t>BCIO:015378</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -23597,7 +23597,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>BCIO:015399</t>
+          <t>BCIO:015379</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -23648,7 +23648,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>BCIO:015400</t>
+          <t>BCIO:015380</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -23699,7 +23699,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>BCIO:015401</t>
+          <t>BCIO:015381</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -23750,7 +23750,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BCIO:015402</t>
+          <t>BCIO:015382</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -23801,7 +23801,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>BCIO:015403</t>
+          <t>BCIO:015383</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -23852,7 +23852,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BCIO:015404</t>
+          <t>BCIO:015384</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -23903,7 +23903,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BCIO:015405</t>
+          <t>BCIO:015385</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -23954,7 +23954,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>BCIO:015406</t>
+          <t>BCIO:015386</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -24005,7 +24005,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>BCIO:015410</t>
+          <t>BCIO:015387</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>BCIO:015411</t>
+          <t>BCIO:015388</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -24107,7 +24107,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>BCIO:015412</t>
+          <t>BCIO:015389</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -24158,7 +24158,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>BCIO:015413</t>
+          <t>BCIO:015390</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -24209,7 +24209,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>BCIO:015414</t>
+          <t>BCIO:015391</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -24260,7 +24260,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>BCIO:015415</t>
+          <t>BCIO:015392</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -24311,7 +24311,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>BCIO:015416</t>
+          <t>BCIO:015393</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -24362,7 +24362,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>BCIO:015417</t>
+          <t>BCIO:015394</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -24413,7 +24413,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>BCIO:015418</t>
+          <t>BCIO:015395</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -24464,7 +24464,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>BCIO:015419</t>
+          <t>BCIO:015396</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -24515,7 +24515,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>BCIO:015420</t>
+          <t>BCIO:015397</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BCIO:015421</t>
+          <t>BCIO:015398</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -24617,7 +24617,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>BCIO:015422</t>
+          <t>BCIO:015399</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -24668,7 +24668,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>BCIO:015423</t>
+          <t>BCIO:015400</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -24719,7 +24719,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>BCIO:015424</t>
+          <t>BCIO:015401</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>BCIO:015425</t>
+          <t>BCIO:015402</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -24821,7 +24821,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>BCIO:015426</t>
+          <t>BCIO:015403</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -24872,7 +24872,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>BCIO:015427</t>
+          <t>BCIO:015404</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -24923,7 +24923,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>BCIO:015428</t>
+          <t>BCIO:015405</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -24974,7 +24974,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>BCIO:015429</t>
+          <t>BCIO:015406</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -25025,7 +25025,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>BCIO:015431</t>
+          <t>BCIO:015407</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -25076,7 +25076,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>BCIO:015439</t>
+          <t>BCIO:015415</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -25127,7 +25127,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>BCIO:015440</t>
+          <t>BCIO:015416</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -25178,7 +25178,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>BCIO:015441</t>
+          <t>BCIO:015417</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -25229,7 +25229,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>BCIO:015442</t>
+          <t>BCIO:015418</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -25280,7 +25280,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>BCIO:015443</t>
+          <t>BCIO:015419</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -25331,7 +25331,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>BCIO:015444</t>
+          <t>BCIO:015420</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -25382,7 +25382,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>BCIO:015445</t>
+          <t>BCIO:015421</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -25433,7 +25433,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>BCIO:015446</t>
+          <t>BCIO:015422</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>BCIO:015447</t>
+          <t>BCIO:015423</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -25535,7 +25535,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>BCIO:015448</t>
+          <t>BCIO:015424</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -25586,7 +25586,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BCIO:015449</t>
+          <t>BCIO:015425</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -25637,7 +25637,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>BCIO:015450</t>
+          <t>BCIO:015426</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -25688,7 +25688,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>BCIO:015451</t>
+          <t>BCIO:015427</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -25739,7 +25739,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BCIO:015452</t>
+          <t>BCIO:015428</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -25790,7 +25790,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>BCIO:015453</t>
+          <t>BCIO:015429</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -25841,7 +25841,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>BCIO:015454</t>
+          <t>BCIO:015431</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -25892,7 +25892,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>BCIO:015455</t>
+          <t>BCIO:015432</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -25943,7 +25943,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>BCIO:015456</t>
+          <t>BCIO:015433</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -25994,7 +25994,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>BCIO:015457</t>
+          <t>BCIO:015434</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -26045,7 +26045,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>BCIO:015458</t>
+          <t>BCIO:015435</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -26096,7 +26096,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>BCIO:015459</t>
+          <t>BCIO:015436</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -26147,7 +26147,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>BCIO:015460</t>
+          <t>BCIO:015437</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>BCIO:015461</t>
+          <t>BCIO:015438</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -26249,7 +26249,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>BCIO:015465</t>
+          <t>BCIO:015442</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -26300,7 +26300,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>BCIO:015466</t>
+          <t>BCIO:015443</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -26351,7 +26351,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>BCIO:015467</t>
+          <t>BCIO:015444</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -26402,7 +26402,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>BCIO:015468</t>
+          <t>BCIO:015445</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -26453,7 +26453,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>BCIO:015469</t>
+          <t>BCIO:015446</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -26504,7 +26504,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>BCIO:015470</t>
+          <t>BCIO:015447</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -26555,7 +26555,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>BCIO:015471</t>
+          <t>BCIO:015448</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -26606,7 +26606,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>BCIO:015472</t>
+          <t>BCIO:015449</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -26657,7 +26657,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>BCIO:015473</t>
+          <t>BCIO:015450</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -26708,7 +26708,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>BCIO:015474</t>
+          <t>BCIO:015451</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -26759,7 +26759,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>BCIO:015475</t>
+          <t>BCIO:015452</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -26810,7 +26810,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>BCIO:015476</t>
+          <t>BCIO:015453</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -26861,7 +26861,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>BCIO:015477</t>
+          <t>BCIO:015454</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>BCIO:015478</t>
+          <t>BCIO:015455</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -26963,7 +26963,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>BCIO:015479</t>
+          <t>BCIO:015456</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -27014,7 +27014,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>BCIO:015480</t>
+          <t>BCIO:015457</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -27065,7 +27065,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>BCIO:015481</t>
+          <t>BCIO:015458</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -27116,7 +27116,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>BCIO:015482</t>
+          <t>BCIO:015459</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -27167,7 +27167,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>BCIO:015483</t>
+          <t>BCIO:015460</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -27218,7 +27218,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>BCIO:015484</t>
+          <t>BCIO:015461</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -27269,7 +27269,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>BCIO:015488</t>
+          <t>BCIO:015462</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -27320,7 +27320,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>BCIO:015489</t>
+          <t>BCIO:015463</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -27371,7 +27371,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>BCIO:015490</t>
+          <t>BCIO:015464</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -27422,7 +27422,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>BCIO:015491</t>
+          <t>BCIO:015465</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -27473,7 +27473,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>BCIO:015492</t>
+          <t>BCIO:015466</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -27524,7 +27524,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>BCIO:015493</t>
+          <t>BCIO:015467</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -27575,7 +27575,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>BCIO:015497</t>
+          <t>BCIO:015471</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>BCIO:015498</t>
+          <t>BCIO:015472</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -27677,7 +27677,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>BCIO:015499</t>
+          <t>BCIO:015473</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -27728,7 +27728,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>BCIO:015500</t>
+          <t>BCIO:015474</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -27779,7 +27779,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>BCIO:015501</t>
+          <t>BCIO:015475</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -27830,7 +27830,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>BCIO:015502</t>
+          <t>BCIO:015476</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -27881,7 +27881,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>BCIO:015503</t>
+          <t>BCIO:015477</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -27932,7 +27932,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>BCIO:015504</t>
+          <t>BCIO:015478</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -27983,7 +27983,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>BCIO:015505</t>
+          <t>BCIO:015479</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -28034,7 +28034,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>BCIO:015506</t>
+          <t>BCIO:015480</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -28085,7 +28085,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>BCIO:015507</t>
+          <t>BCIO:015481</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -28136,7 +28136,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>BCIO:015508</t>
+          <t>BCIO:015482</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -28187,7 +28187,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>BCIO:015509</t>
+          <t>BCIO:015483</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -28238,7 +28238,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>BCIO:015510</t>
+          <t>BCIO:015484</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -28289,7 +28289,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>BCIO:015511</t>
+          <t>BCIO:015485</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>BCIO:015512</t>
+          <t>BCIO:015486</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -28391,7 +28391,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>BCIO:015513</t>
+          <t>BCIO:015487</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -28442,7 +28442,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>BCIO:015514</t>
+          <t>BCIO:015488</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -28493,7 +28493,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>BCIO:015515</t>
+          <t>BCIO:015489</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -28544,7 +28544,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>BCIO:015516</t>
+          <t>BCIO:015490</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -28595,7 +28595,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>BCIO:015517</t>
+          <t>BCIO:015491</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>BCIO:015518</t>
+          <t>BCIO:015492</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -28697,7 +28697,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>BCIO:015519</t>
+          <t>BCIO:015493</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -28748,7 +28748,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>BCIO:015520</t>
+          <t>BCIO:015494</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -28799,7 +28799,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>BCIO:015521</t>
+          <t>BCIO:015495</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -28850,7 +28850,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>BCIO:015522</t>
+          <t>BCIO:015496</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -28901,7 +28901,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>BCIO:015523</t>
+          <t>BCIO:015497</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -28952,7 +28952,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>BCIO:015524</t>
+          <t>BCIO:015498</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -29003,7 +29003,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>BCIO:015525</t>
+          <t>BCIO:015499</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>BCIO:015529</t>
+          <t>BCIO:015500</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -29105,7 +29105,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>BCIO:015530</t>
+          <t>BCIO:015501</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -29156,7 +29156,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>BCIO:015531</t>
+          <t>BCIO:015502</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -29207,7 +29207,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>BCIO:015532</t>
+          <t>BCIO:015503</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -29258,7 +29258,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>BCIO:015533</t>
+          <t>BCIO:015504</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -29309,7 +29309,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>BCIO:015534</t>
+          <t>BCIO:015505</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -29360,7 +29360,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BCIO:015535</t>
+          <t>BCIO:015506</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -29411,7 +29411,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>BCIO:015536</t>
+          <t>BCIO:015507</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -29462,7 +29462,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BCIO:015537</t>
+          <t>BCIO:015508</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -29513,7 +29513,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>BCIO:015538</t>
+          <t>BCIO:015509</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -29564,7 +29564,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>BCIO:015539</t>
+          <t>BCIO:015510</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -29615,7 +29615,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>BCIO:015540</t>
+          <t>BCIO:015511</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -29666,7 +29666,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>BCIO:015541</t>
+          <t>BCIO:015512</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -29717,7 +29717,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>BCIO:015542</t>
+          <t>BCIO:015513</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>BCIO:015543</t>
+          <t>BCIO:015514</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -29819,7 +29819,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>BCIO:015544</t>
+          <t>BCIO:015515</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -29870,7 +29870,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>BCIO:015545</t>
+          <t>BCIO:015516</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -29921,7 +29921,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>BCIO:015546</t>
+          <t>BCIO:015517</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -29972,7 +29972,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>BCIO:015547</t>
+          <t>BCIO:015518</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -30023,7 +30023,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>BCIO:015548</t>
+          <t>BCIO:015519</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -30074,7 +30074,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>BCIO:015549</t>
+          <t>BCIO:015520</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -30125,7 +30125,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>BCIO:015550</t>
+          <t>BCIO:015521</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -30176,7 +30176,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>BCIO:015551</t>
+          <t>BCIO:015522</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -30227,7 +30227,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>BCIO:015552</t>
+          <t>BCIO:015523</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -30278,7 +30278,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>BCIO:015553</t>
+          <t>BCIO:015524</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -30329,7 +30329,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>BCIO:015554</t>
+          <t>BCIO:015525</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -30380,7 +30380,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>BCIO:015555</t>
+          <t>BCIO:015526</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -30431,7 +30431,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>BCIO:015556</t>
+          <t>BCIO:015527</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>BCIO:015557</t>
+          <t>BCIO:015528</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -30533,7 +30533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>BCIO:015558</t>
+          <t>BCIO:015529</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -30584,7 +30584,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>BCIO:015559</t>
+          <t>BCIO:015530</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -30635,7 +30635,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>BCIO:015560</t>
+          <t>BCIO:015531</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -30686,7 +30686,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>BCIO:015561</t>
+          <t>BCIO:015532</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -30737,7 +30737,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>BCIO:015562</t>
+          <t>BCIO:015533</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -30788,7 +30788,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>BCIO:015563</t>
+          <t>BCIO:015534</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -30839,7 +30839,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>BCIO:015564</t>
+          <t>BCIO:015535</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -30890,7 +30890,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>BCIO:015565</t>
+          <t>BCIO:015536</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -30941,7 +30941,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>BCIO:015566</t>
+          <t>BCIO:015537</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -30992,7 +30992,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>BCIO:015567</t>
+          <t>BCIO:015538</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -31043,7 +31043,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>BCIO:015568</t>
+          <t>BCIO:015539</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -31094,7 +31094,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>BCIO:015569</t>
+          <t>BCIO:015540</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -31145,7 +31145,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>BCIO:015570</t>
+          <t>BCIO:015541</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>BCIO:015571</t>
+          <t>BCIO:015542</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -31247,7 +31247,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>BCIO:015572</t>
+          <t>BCIO:015543</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -31298,7 +31298,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>BCIO:015573</t>
+          <t>BCIO:015544</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -31349,7 +31349,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>BCIO:015574</t>
+          <t>BCIO:015545</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -31400,7 +31400,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>BCIO:015575</t>
+          <t>BCIO:015546</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -31451,7 +31451,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>BCIO:015576</t>
+          <t>BCIO:015547</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -31502,7 +31502,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>BCIO:015577</t>
+          <t>BCIO:015548</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -31553,7 +31553,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>BCIO:015578</t>
+          <t>BCIO:015549</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -31604,7 +31604,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>BCIO:015579</t>
+          <t>BCIO:015550</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -31655,7 +31655,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>BCIO:015580</t>
+          <t>BCIO:015551</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -31706,7 +31706,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>BCIO:015581</t>
+          <t>BCIO:015552</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -31757,7 +31757,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>BCIO:015582</t>
+          <t>BCIO:015553</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -31808,7 +31808,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>BCIO:015583</t>
+          <t>BCIO:015554</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -31859,7 +31859,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>BCIO:015584</t>
+          <t>BCIO:015555</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>BCIO:015585</t>
+          <t>BCIO:015556</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -31961,7 +31961,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>BCIO:015586</t>
+          <t>BCIO:015557</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -32012,7 +32012,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>BCIO:015587</t>
+          <t>BCIO:015558</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -32063,7 +32063,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>BCIO:015588</t>
+          <t>BCIO:015559</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -32114,7 +32114,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>BCIO:015589</t>
+          <t>BCIO:015560</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -32165,7 +32165,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>BCIO:015590</t>
+          <t>BCIO:015561</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -32216,7 +32216,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>BCIO:015591</t>
+          <t>BCIO:015562</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -32267,7 +32267,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>BCIO:015592</t>
+          <t>BCIO:015563</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -32318,7 +32318,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>BCIO:015593</t>
+          <t>BCIO:015564</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -32369,7 +32369,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>BCIO:015594</t>
+          <t>BCIO:015565</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -32420,7 +32420,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>BCIO:015595</t>
+          <t>BCIO:015566</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -32471,7 +32471,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>BCIO:015596</t>
+          <t>BCIO:015567</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -32522,7 +32522,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>BCIO:015597</t>
+          <t>BCIO:015568</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -32573,7 +32573,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>BCIO:015598</t>
+          <t>BCIO:015569</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>BCIO:015599</t>
+          <t>BCIO:015570</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -32675,7 +32675,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>BCIO:015600</t>
+          <t>BCIO:015571</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -32726,7 +32726,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>BCIO:015601</t>
+          <t>BCIO:015572</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -32777,7 +32777,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>BCIO:015602</t>
+          <t>BCIO:015573</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -32828,7 +32828,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>BCIO:015603</t>
+          <t>BCIO:015574</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -32879,7 +32879,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>BCIO:015604</t>
+          <t>BCIO:015575</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -32930,7 +32930,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>BCIO:015605</t>
+          <t>BCIO:015576</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -32981,7 +32981,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>BCIO:015606</t>
+          <t>BCIO:015577</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -33032,7 +33032,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>BCIO:015607</t>
+          <t>BCIO:015578</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -33083,7 +33083,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>BCIO:015608</t>
+          <t>BCIO:015579</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -33134,7 +33134,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>BCIO:015609</t>
+          <t>BCIO:015580</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -33185,7 +33185,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>BCIO:015610</t>
+          <t>BCIO:015581</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -33236,7 +33236,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>BCIO:015611</t>
+          <t>BCIO:015582</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -33287,7 +33287,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>BCIO:015612</t>
+          <t>BCIO:015583</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>BCIO:015620</t>
+          <t>BCIO:015591</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -33389,7 +33389,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>BCIO:015621</t>
+          <t>BCIO:015592</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -33440,7 +33440,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>BCIO:015622</t>
+          <t>BCIO:015593</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -33491,7 +33491,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>BCIO:015623</t>
+          <t>BCIO:015594</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -33542,7 +33542,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>BCIO:015624</t>
+          <t>BCIO:015595</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -33593,7 +33593,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>BCIO:015625</t>
+          <t>BCIO:015596</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -33644,7 +33644,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>BCIO:015626</t>
+          <t>BCIO:015597</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -33695,7 +33695,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>BCIO:015627</t>
+          <t>BCIO:015598</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -33746,7 +33746,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>BCIO:015628</t>
+          <t>BCIO:015599</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -33797,7 +33797,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>BCIO:015629</t>
+          <t>BCIO:015600</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -33848,7 +33848,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>BCIO:015630</t>
+          <t>BCIO:015601</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -33899,7 +33899,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>BCIO:015631</t>
+          <t>BCIO:015602</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -33950,7 +33950,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>BCIO:015632</t>
+          <t>BCIO:015603</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -34001,7 +34001,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>BCIO:015633</t>
+          <t>BCIO:015604</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>BCIO:015634</t>
+          <t>BCIO:015605</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -34103,7 +34103,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>BCIO:015635</t>
+          <t>BCIO:015606</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -34154,7 +34154,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>BCIO:015636</t>
+          <t>BCIO:015607</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -34205,7 +34205,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>BCIO:015637</t>
+          <t>BCIO:015608</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -34256,7 +34256,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>BCIO:015638</t>
+          <t>BCIO:015609</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -34307,7 +34307,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>BCIO:015639</t>
+          <t>BCIO:015610</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -34358,7 +34358,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>BCIO:015640</t>
+          <t>BCIO:015611</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -34409,7 +34409,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>BCIO:015641</t>
+          <t>BCIO:015612</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -34460,7 +34460,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>BCIO:015642</t>
+          <t>BCIO:015613</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -34511,7 +34511,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>BCIO:015643</t>
+          <t>BCIO:015614</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -34562,7 +34562,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>BCIO:015644</t>
+          <t>BCIO:015615</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -34613,7 +34613,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>BCIO:015645</t>
+          <t>BCIO:015616</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -34664,7 +34664,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>BCIO:015646</t>
+          <t>BCIO:015617</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -34715,7 +34715,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>BCIO:015647</t>
+          <t>BCIO:015618</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>BCIO:015648</t>
+          <t>BCIO:015619</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -34817,7 +34817,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>BCIO:015649</t>
+          <t>BCIO:015620</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -34868,7 +34868,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>BCIO:015650</t>
+          <t>BCIO:015621</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -34919,7 +34919,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>BCIO:015651</t>
+          <t>BCIO:015622</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -34970,7 +34970,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>BCIO:015652</t>
+          <t>BCIO:015623</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -35021,7 +35021,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>BCIO:015653</t>
+          <t>BCIO:015624</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -35072,7 +35072,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>BCIO:015654</t>
+          <t>BCIO:015625</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -35123,7 +35123,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>BCIO:015655</t>
+          <t>BCIO:015626</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -35174,7 +35174,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>BCIO:015656</t>
+          <t>BCIO:015627</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -35225,7 +35225,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>BCIO:015657</t>
+          <t>BCIO:015628</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -35276,7 +35276,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>BCIO:015658</t>
+          <t>BCIO:015629</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -35327,7 +35327,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>BCIO:015659</t>
+          <t>BCIO:015630</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -35378,7 +35378,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>BCIO:015660</t>
+          <t>BCIO:015631</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -35429,7 +35429,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>BCIO:015661</t>
+          <t>BCIO:015632</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>BCIO:015662</t>
+          <t>BCIO:015633</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -35531,7 +35531,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>BCIO:015663</t>
+          <t>BCIO:015634</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -35582,7 +35582,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>BCIO:015664</t>
+          <t>BCIO:015635</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -35633,7 +35633,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>BCIO:015665</t>
+          <t>BCIO:015636</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -35684,7 +35684,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>BCIO:015666</t>
+          <t>BCIO:015637</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -35735,7 +35735,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>BCIO:015667</t>
+          <t>BCIO:015638</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -35786,7 +35786,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>BCIO:015668</t>
+          <t>BCIO:015639</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -35837,7 +35837,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>BCIO:015669</t>
+          <t>BCIO:015640</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -35888,7 +35888,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>BCIO:015670</t>
+          <t>BCIO:015641</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -35939,7 +35939,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>BCIO:015671</t>
+          <t>BCIO:015642</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -35990,7 +35990,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>BCIO:015672</t>
+          <t>BCIO:015643</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -36041,7 +36041,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>BCIO:015673</t>
+          <t>BCIO:015644</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -36092,7 +36092,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>BCIO:015674</t>
+          <t>BCIO:015645</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -36143,7 +36143,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>BCIO:015675</t>
+          <t>BCIO:015646</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>BCIO:015676</t>
+          <t>BCIO:015647</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -36245,7 +36245,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>BCIO:015677</t>
+          <t>BCIO:015648</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -36296,7 +36296,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>BCIO:015678</t>
+          <t>BCIO:015649</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -36347,7 +36347,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>BCIO:015679</t>
+          <t>BCIO:015650</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -36398,7 +36398,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>BCIO:015680</t>
+          <t>BCIO:015651</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -36449,7 +36449,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>BCIO:015681</t>
+          <t>BCIO:015652</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -36500,7 +36500,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>BCIO:015682</t>
+          <t>BCIO:015653</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -36551,7 +36551,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>BCIO:015683</t>
+          <t>BCIO:015654</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -36602,7 +36602,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>BCIO:015684</t>
+          <t>BCIO:015655</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -36653,7 +36653,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>BCIO:015685</t>
+          <t>BCIO:015656</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -36704,7 +36704,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>BCIO:015686</t>
+          <t>BCIO:015657</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -36755,7 +36755,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>BCIO:015687</t>
+          <t>BCIO:015658</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -36806,7 +36806,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>BCIO:015688</t>
+          <t>BCIO:015659</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -36857,7 +36857,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>BCIO:015689</t>
+          <t>BCIO:015660</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>BCIO:015690</t>
+          <t>BCIO:015661</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -36959,7 +36959,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>BCIO:015691</t>
+          <t>BCIO:015662</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -37010,7 +37010,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>BCIO:015692</t>
+          <t>BCIO:015663</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -37061,7 +37061,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>BCIO:015693</t>
+          <t>BCIO:015664</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -37112,7 +37112,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>BCIO:015694</t>
+          <t>BCIO:015665</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -37163,7 +37163,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>BCIO:015695</t>
+          <t>BCIO:015666</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -37214,7 +37214,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>BCIO:015696</t>
+          <t>BCIO:015667</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -37265,7 +37265,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>BCIO:015697</t>
+          <t>BCIO:015668</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -37316,7 +37316,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>BCIO:015698</t>
+          <t>BCIO:015669</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -37367,7 +37367,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>BCIO:015699</t>
+          <t>BCIO:015670</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -37418,7 +37418,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>BCIO:015700</t>
+          <t>BCIO:015671</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -37469,7 +37469,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>BCIO:015701</t>
+          <t>BCIO:015672</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -37520,7 +37520,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>BCIO:015702</t>
+          <t>BCIO:015673</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -37571,7 +37571,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>BCIO:015703</t>
+          <t>BCIO:015674</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>BCIO:015704</t>
+          <t>BCIO:015675</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -37673,7 +37673,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>BCIO:015705</t>
+          <t>BCIO:015676</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -37724,7 +37724,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>BCIO:015706</t>
+          <t>BCIO:015677</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -37775,7 +37775,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>BCIO:015707</t>
+          <t>BCIO:015678</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -37826,7 +37826,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>BCIO:015708</t>
+          <t>BCIO:015679</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -37877,7 +37877,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>BCIO:015709</t>
+          <t>BCIO:015680</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -37928,7 +37928,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>BCIO:015710</t>
+          <t>BCIO:015681</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -37979,7 +37979,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>BCIO:015711</t>
+          <t>BCIO:015682</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -38030,7 +38030,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>BCIO:015712</t>
+          <t>BCIO:015683</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -38081,7 +38081,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>BCIO:015713</t>
+          <t>BCIO:015684</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -38132,7 +38132,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>BCIO:015714</t>
+          <t>BCIO:015685</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -38183,7 +38183,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>BCIO:015715</t>
+          <t>BCIO:015686</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -38234,7 +38234,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>BCIO:015716</t>
+          <t>BCIO:015687</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -38285,7 +38285,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>BCIO:015717</t>
+          <t>BCIO:015688</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>BCIO:015718</t>
+          <t>BCIO:015689</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -38387,7 +38387,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>BCIO:015719</t>
+          <t>BCIO:015690</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -38438,7 +38438,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>BCIO:015720</t>
+          <t>BCIO:015691</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -38489,7 +38489,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>BCIO:015721</t>
+          <t>BCIO:015692</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -38540,7 +38540,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>BCIO:015722</t>
+          <t>BCIO:015693</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -38591,7 +38591,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>BCIO:015723</t>
+          <t>BCIO:015694</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -38642,7 +38642,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>BCIO:015724</t>
+          <t>BCIO:015695</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -38693,7 +38693,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>BCIO:015725</t>
+          <t>BCIO:015696</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -38744,7 +38744,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>BCIO:015726</t>
+          <t>BCIO:015697</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -38795,7 +38795,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>BCIO:015727</t>
+          <t>BCIO:015698</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -38846,7 +38846,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>BCIO:015728</t>
+          <t>BCIO:015699</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -38897,7 +38897,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>BCIO:015729</t>
+          <t>BCIO:015700</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -38948,7 +38948,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>BCIO:015730</t>
+          <t>BCIO:015701</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -38999,7 +38999,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>BCIO:015731</t>
+          <t>BCIO:015702</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>BCIO:015732</t>
+          <t>BCIO:015703</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -39101,7 +39101,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>BCIO:015733</t>
+          <t>BCIO:015704</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -39152,7 +39152,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>BCIO:015734</t>
+          <t>BCIO:015705</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -39203,7 +39203,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>BCIO:015735</t>
+          <t>BCIO:015706</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -39254,7 +39254,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>BCIO:015736</t>
+          <t>BCIO:015707</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -39305,7 +39305,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>BCIO:015740</t>
+          <t>BCIO:015708</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -39356,7 +39356,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>BCIO:015741</t>
+          <t>BCIO:015709</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -39407,7 +39407,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>BCIO:015742</t>
+          <t>BCIO:015710</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -39458,7 +39458,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>BCIO:015743</t>
+          <t>BCIO:015711</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -39509,7 +39509,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>BCIO:015744</t>
+          <t>BCIO:015712</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -39560,7 +39560,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>BCIO:015745</t>
+          <t>BCIO:015713</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -39611,7 +39611,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>BCIO:015746</t>
+          <t>BCIO:015714</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -39662,7 +39662,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>BCIO:015747</t>
+          <t>BCIO:015715</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -39713,7 +39713,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>BCIO:015748</t>
+          <t>BCIO:015716</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>BCIO:015749</t>
+          <t>BCIO:015717</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -39815,7 +39815,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>BCIO:015750</t>
+          <t>BCIO:015718</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -39866,7 +39866,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>BCIO:015751</t>
+          <t>BCIO:015719</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -39917,7 +39917,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>BCIO:015752</t>
+          <t>BCIO:015720</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -39968,7 +39968,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>BCIO:015753</t>
+          <t>BCIO:015721</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -40019,7 +40019,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>BCIO:015754</t>
+          <t>BCIO:015722</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -40070,7 +40070,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>BCIO:015755</t>
+          <t>BCIO:015723</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -40121,7 +40121,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>BCIO:015756</t>
+          <t>BCIO:015724</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -40172,7 +40172,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>BCIO:015757</t>
+          <t>BCIO:015725</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -40223,7 +40223,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>BCIO:015860</t>
+          <t>BCIO:015836</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -40274,7 +40274,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>BCIO:015861</t>
+          <t>BCIO:015837</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -40325,7 +40325,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>BCIO:015862</t>
+          <t>BCIO:015838</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -40376,7 +40376,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>BCIO:015863</t>
+          <t>BCIO:015839</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -40427,7 +40427,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>BCIO:015864</t>
+          <t>BCIO:015840</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>BCIO:015865</t>
+          <t>BCIO:015841</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -40529,7 +40529,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>BCIO:015866</t>
+          <t>BCIO:015842</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -40580,7 +40580,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>BCIO:015867</t>
+          <t>BCIO:015843</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -40631,7 +40631,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>BCIO:015766</t>
+          <t>BCIO:015734</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -40682,7 +40682,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>BCIO:015767</t>
+          <t>BCIO:015735</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -40733,7 +40733,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>BCIO:015768</t>
+          <t>BCIO:015736</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -40784,7 +40784,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>BCIO:015769</t>
+          <t>BCIO:015737</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -40835,7 +40835,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>BCIO:015770</t>
+          <t>BCIO:015738</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -40886,7 +40886,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>BCIO:015771</t>
+          <t>BCIO:015739</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -40937,7 +40937,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>BCIO:015772</t>
+          <t>BCIO:015740</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -40988,7 +40988,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>BCIO:015773</t>
+          <t>BCIO:015741</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -41039,7 +41039,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>BCIO:015774</t>
+          <t>BCIO:015742</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -41090,7 +41090,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>BCIO:015775</t>
+          <t>BCIO:015743</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -41141,7 +41141,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>BCIO:015776</t>
+          <t>BCIO:015744</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>BCIO:015777</t>
+          <t>BCIO:015745</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -41243,7 +41243,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>BCIO:015778</t>
+          <t>BCIO:015746</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -41294,7 +41294,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>BCIO:015779</t>
+          <t>BCIO:015747</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -41345,7 +41345,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>BCIO:015780</t>
+          <t>BCIO:015748</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -41396,7 +41396,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>BCIO:015781</t>
+          <t>BCIO:015749</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -41447,7 +41447,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>BCIO:015782</t>
+          <t>BCIO:015750</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -41498,7 +41498,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>BCIO:015783</t>
+          <t>BCIO:015751</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -41549,7 +41549,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>BCIO:015784</t>
+          <t>BCIO:015752</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -41600,7 +41600,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>BCIO:015785</t>
+          <t>BCIO:015753</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -41651,7 +41651,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>BCIO:015786</t>
+          <t>BCIO:015754</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -41702,7 +41702,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>BCIO:015787</t>
+          <t>BCIO:015755</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -41753,7 +41753,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>BCIO:015788</t>
+          <t>BCIO:015756</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -41804,7 +41804,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>BCIO:015789</t>
+          <t>BCIO:015757</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -41855,7 +41855,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>BCIO:015790</t>
+          <t>BCIO:015758</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>BCIO:015791</t>
+          <t>BCIO:015759</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -41957,7 +41957,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>BCIO:015792</t>
+          <t>BCIO:015760</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -42008,7 +42008,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>BCIO:015793</t>
+          <t>BCIO:015761</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -42059,7 +42059,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>BCIO:015794</t>
+          <t>BCIO:015762</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -42110,7 +42110,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>BCIO:015795</t>
+          <t>BCIO:015763</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -42161,7 +42161,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>BCIO:015796</t>
+          <t>BCIO:015764</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -42212,7 +42212,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>BCIO:015797</t>
+          <t>BCIO:015765</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -42263,7 +42263,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>BCIO:015798</t>
+          <t>BCIO:015766</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -42314,7 +42314,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>BCIO:015799</t>
+          <t>BCIO:015767</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -42365,7 +42365,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>BCIO:015800</t>
+          <t>BCIO:015768</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -42416,7 +42416,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>BCIO:015801</t>
+          <t>BCIO:015769</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -42467,7 +42467,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>BCIO:015868</t>
+          <t>BCIO:015844</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -42518,7 +42518,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>BCIO:015869</t>
+          <t>BCIO:015845</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -42569,7 +42569,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>BCIO:015870</t>
+          <t>BCIO:015846</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>BCIO:015802</t>
+          <t>BCIO:015770</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -42671,7 +42671,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>BCIO:015803</t>
+          <t>BCIO:015771</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -42722,7 +42722,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>BCIO:015804</t>
+          <t>BCIO:015772</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -42773,7 +42773,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>BCIO:015805</t>
+          <t>BCIO:015773</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -42824,7 +42824,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>BCIO:015806</t>
+          <t>BCIO:015774</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -42875,7 +42875,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>BCIO:015807</t>
+          <t>BCIO:015775</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -42926,7 +42926,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>BCIO:015808</t>
+          <t>BCIO:015776</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -42977,7 +42977,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>BCIO:015809</t>
+          <t>BCIO:015777</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -43028,7 +43028,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>BCIO:015810</t>
+          <t>BCIO:015778</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -43079,7 +43079,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>BCIO:015811</t>
+          <t>BCIO:015779</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -43130,7 +43130,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>BCIO:015812</t>
+          <t>BCIO:015780</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -43181,7 +43181,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>BCIO:015813</t>
+          <t>BCIO:015781</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -43232,7 +43232,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>BCIO:015814</t>
+          <t>BCIO:015782</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -43283,7 +43283,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>BCIO:015815</t>
+          <t>BCIO:015783</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>BCIO:015816</t>
+          <t>BCIO:015784</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -43385,7 +43385,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>BCIO:015820</t>
+          <t>BCIO:015785</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -43436,7 +43436,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>BCIO:015821</t>
+          <t>BCIO:015786</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -43487,7 +43487,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>BCIO:015822</t>
+          <t>BCIO:015787</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -43538,7 +43538,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>BCIO:015823</t>
+          <t>BCIO:015788</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -43589,7 +43589,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>BCIO:015824</t>
+          <t>BCIO:015789</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -43640,7 +43640,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>BCIO:015825</t>
+          <t>BCIO:015790</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -43691,7 +43691,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>BCIO:015826</t>
+          <t>BCIO:015791</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -43742,7 +43742,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>BCIO:015827</t>
+          <t>BCIO:015792</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -43793,7 +43793,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>BCIO:015828</t>
+          <t>BCIO:015793</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -43844,7 +43844,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>BCIO:015829</t>
+          <t>BCIO:015794</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -43895,7 +43895,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>BCIO:015830</t>
+          <t>BCIO:015795</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -43946,7 +43946,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>BCIO:015831</t>
+          <t>BCIO:015796</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -43997,7 +43997,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>BCIO:015832</t>
+          <t>BCIO:015797</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>BCIO:015833</t>
+          <t>BCIO:015798</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -44099,7 +44099,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>BCIO:015840</t>
+          <t>BCIO:015802</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -44150,7 +44150,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>BCIO:015841</t>
+          <t>BCIO:015803</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -44201,7 +44201,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>BCIO:015842</t>
+          <t>BCIO:015804</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -44252,7 +44252,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>BCIO:015843</t>
+          <t>BCIO:015805</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -44303,7 +44303,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>BCIO:015844</t>
+          <t>BCIO:015806</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -44354,7 +44354,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>BCIO:015845</t>
+          <t>BCIO:015807</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -44405,32 +44405,27 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>BCIO:015432</t>
+          <t>OPMI:0000121</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>household income population statistic</t>
+          <t>socioeconomic status</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>A population statistic about household income.</t>
+          <t xml:space="preserve">A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.  </t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>population statistic</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="K899" t="inlineStr">
         <is>
           <t>population</t>
-        </is>
-      </c>
-      <c r="M899" t="inlineStr">
-        <is>
-          <t>household income</t>
         </is>
       </c>
       <c r="R899" t="inlineStr">
@@ -44442,22 +44437,22 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>BCIO:015433</t>
+          <t>BCIO:015408</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>mean household income population statistic</t>
+          <t>household income population statistic</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the mean value of household income in the population.</t>
+          <t>A population statistic about household income.</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>household income population statistic</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="K900" t="inlineStr">
@@ -44479,17 +44474,17 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>BCIO:015434</t>
+          <t>BCIO:015409</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>minimum household income population statistic</t>
+          <t>mean household income population statistic</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the minimum value of household income in the population.</t>
+          <t>A(n) household income population statistic that is the mean value of household income in the population.</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -44516,17 +44511,17 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>BCIO:015435</t>
+          <t>BCIO:015410</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>maximum household income population statistic</t>
+          <t>minimum household income population statistic</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the maximum value of household income in the population.</t>
+          <t>A(n) household income population statistic that is the minimum value of household income in the population.</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -44553,17 +44548,17 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>BCIO:015436</t>
+          <t>BCIO:015411</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>median household income population statistic</t>
+          <t>maximum household income population statistic</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the median value of household income in the population.</t>
+          <t>A(n) household income population statistic that is the maximum value of household income in the population.</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -44590,17 +44585,17 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>BCIO:015437</t>
+          <t>BCIO:015412</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>percentage household income population statistic</t>
+          <t>median household income population statistic</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the percentage value of household income in the population.</t>
+          <t>A(n) household income population statistic that is the median value of household income in the population.</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -44627,17 +44622,17 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>BCIO:015438</t>
+          <t>BCIO:015413</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>proportion household income population statistic</t>
+          <t>percentage household income population statistic</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the proportion of individuals having a household income in the population.</t>
+          <t>A(n) household income population statistic that is the percentage value of household income in the population.</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -44664,22 +44659,22 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>BCIO:015462</t>
+          <t>BCIO:015414</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>income-related welfare benefit population statistic</t>
+          <t>proportion household income population statistic</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>A population statistic about income-related welfare benefit.</t>
+          <t>A(n) household income population statistic that is the proportion of individuals having a household income in the population.</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>individual income population statistic</t>
+          <t>household income population statistic</t>
         </is>
       </c>
       <c r="K906" t="inlineStr">
@@ -44689,7 +44684,7 @@
       </c>
       <c r="M906" t="inlineStr">
         <is>
-          <t>income-related welfare benefit</t>
+          <t>household income</t>
         </is>
       </c>
       <c r="R906" t="inlineStr">
@@ -44701,22 +44696,22 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>BCIO:015463</t>
+          <t>BCIO:015439</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>percentage income-related welfare benefit population statistic</t>
+          <t>income-related welfare benefit population statistic</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>A(n) income-related welfare benefit population statistic that is the percentage of people that have income-related welfare benefit in the population.</t>
+          <t>A population statistic about income-related welfare benefit.</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>income-related welfare benefit population statistic</t>
+          <t>individual income population statistic</t>
         </is>
       </c>
       <c r="K907" t="inlineStr">
@@ -44738,17 +44733,17 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>BCIO:015464</t>
+          <t>BCIO:015440</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>proportion income-related welfare benefit population statistic</t>
+          <t>percentage income-related welfare benefit population statistic</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>A(n) income-related welfare benefit population statistic that is the proportion of people that have income-related welfare benefit in the population.</t>
+          <t>A(n) income-related welfare benefit population statistic that is the percentage of people that have income-related welfare benefit in the population.</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -44775,27 +44770,32 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>OPMI:0000121</t>
+          <t>BCIO:015441</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>socioeconomic status</t>
+          <t>proportion income-related welfare benefit population statistic</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.  </t>
+          <t>A(n) income-related welfare benefit population statistic that is the proportion of people that have income-related welfare benefit in the population.</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>income-related welfare benefit population statistic</t>
         </is>
       </c>
       <c r="K909" t="inlineStr">
         <is>
           <t>population</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>income-related welfare benefit</t>
         </is>
       </c>
       <c r="R909" t="inlineStr">
@@ -44807,22 +44807,22 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>BCIO:015304</t>
+          <t>BCIO:015468</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>doctoral student role population statistic</t>
+          <t>insured party role population statistic</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>A population statistic about doctoral student role.</t>
+          <t>A population statistic about insured party role.</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="K910" t="inlineStr">
@@ -44832,7 +44832,7 @@
       </c>
       <c r="M910" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>insured party role</t>
         </is>
       </c>
       <c r="R910" t="inlineStr">
@@ -44844,22 +44844,22 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>BCIO:015305</t>
+          <t>BCIO:015469</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>percentage doctoral student role population statistic</t>
+          <t>percentage insured party role population statistic</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>A(n) doctoral student role population statistic that is the percentage of people that are a doctoral student role in the population.</t>
+          <t>A(n) insured party role population statistic that is the percentage of people that have a insured party role in the population.</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>doctoral student role population statistic</t>
+          <t>insured party role population statistic</t>
         </is>
       </c>
       <c r="K911" t="inlineStr">
@@ -44869,7 +44869,7 @@
       </c>
       <c r="M911" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>insured party role</t>
         </is>
       </c>
       <c r="R911" t="inlineStr">
@@ -44881,22 +44881,22 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>BCIO:015306</t>
+          <t>BCIO:015470</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>proportion doctoral student role population statistic</t>
+          <t>proportion insured party role population statistic</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>A(n) doctoral student role population statistic that is the proportion of people that are a doctoral student role in the population.</t>
+          <t>A(n) insured party role population statistic that is the proportion of people that have a insured party role in the population.</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>doctoral student role population statistic</t>
+          <t>insured party role population statistic</t>
         </is>
       </c>
       <c r="K912" t="inlineStr">
@@ -44906,7 +44906,7 @@
       </c>
       <c r="M912" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>insured party role</t>
         </is>
       </c>
       <c r="R912" t="inlineStr">
@@ -44918,22 +44918,22 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>BCIO:015380</t>
+          <t>BCIO:015584</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>graduate student role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>A population statistic about graduate student role.</t>
+          <t>A population statistic about past behaviour .</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="K913" t="inlineStr">
@@ -44943,7 +44943,7 @@
       </c>
       <c r="M913" t="inlineStr">
         <is>
-          <t>graduate student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R913" t="inlineStr">
@@ -44955,22 +44955,22 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>BCIO:015381</t>
+          <t>BCIO:015585</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>percentage graduate student role population statistic</t>
+          <t>mean past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>A(n) graduate student role population statistic that is the percentage of people that have a graduate student role in the population.</t>
+          <t>A(n) past behaviour  population statistic that is the mean value of past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>graduate student role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K914" t="inlineStr">
@@ -44980,7 +44980,7 @@
       </c>
       <c r="M914" t="inlineStr">
         <is>
-          <t>graduate student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R914" t="inlineStr">
@@ -44992,22 +44992,22 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>BCIO:015382</t>
+          <t>BCIO:015586</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>proportion graduate student role population statistic</t>
+          <t>minimum past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>A(n) graduate student role population statistic that is the proportion of people that have a graduate student role in the population.</t>
+          <t>A(n) past behaviour  population statistic that is the minimum value of past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>graduate student role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K915" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="M915" t="inlineStr">
         <is>
-          <t>graduate student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R915" t="inlineStr">
@@ -45029,22 +45029,22 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>BCIO:015407</t>
+          <t>BCIO:015587</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>maximum past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>A population statistic about higher education student role.</t>
+          <t>A(n) past behaviour  population statistic that is the maximum value of past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>student or trainee role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K916" t="inlineStr">
@@ -45054,7 +45054,7 @@
       </c>
       <c r="M916" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R916" t="inlineStr">
@@ -45066,22 +45066,22 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>BCIO:015408</t>
+          <t>BCIO:015588</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>percentage higher education student role population statistic</t>
+          <t>median past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>A(n) higher education student role population statistic that is the percentage of people that have a higher education student role in the population.</t>
+          <t>A(n) past behaviour  population statistic that is the median value of past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K917" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="M917" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R917" t="inlineStr">
@@ -45103,22 +45103,22 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>BCIO:015409</t>
+          <t>BCIO:015589</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>proportion higher education student role population statistic</t>
+          <t>percentage past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>A(n) higher education student role population statistic that is the proportion of people that have a higher education student role in the population.</t>
+          <t>A(n) past behaviour  population statistic that is the percentage value of past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K918" t="inlineStr">
@@ -45128,7 +45128,7 @@
       </c>
       <c r="M918" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R918" t="inlineStr">
@@ -45140,22 +45140,22 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>BCIO:015485</t>
+          <t>BCIO:015590</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>informal education student role population statistic</t>
+          <t>proportion past behaviour  population statistic</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>A population statistic about informal education student role.</t>
+          <t>A(n) past behaviour  population statistic that is the proportion of individuals having a past behaviour  in the population.</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>student or trainee role population statistic</t>
+          <t>past behaviour  population statistic</t>
         </is>
       </c>
       <c r="K919" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="M919" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="R919" t="inlineStr">
@@ -45177,22 +45177,22 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>BCIO:015486</t>
+          <t>BCIO:015726</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>percentage informal education student role population statistic</t>
+          <t>socioeconomic status category population statistic</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>A(n) informal education student role population statistic that is the percentage of people that have a informal education student role in the population.</t>
+          <t>A population statistic about socioeconomic status category.</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>informal education student role population statistic</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="K920" t="inlineStr">
@@ -45202,7 +45202,7 @@
       </c>
       <c r="M920" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t>socioeconomic status category</t>
         </is>
       </c>
       <c r="R920" t="inlineStr">
@@ -45214,22 +45214,22 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>BCIO:015487</t>
+          <t>BCIO:015727</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>proportion informal education student role population statistic</t>
+          <t>percentage socioeconomic status category population statistic</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>A(n) informal education student role population statistic that is the proportion of people that have a informal education student role in the population.</t>
+          <t>A(n) socioeconomic status category population statistic that is the percentage of people that have a socioeconomic status category in the population.</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>informal education student role population statistic</t>
+          <t>socioeconomic status category population statistic</t>
         </is>
       </c>
       <c r="K921" t="inlineStr">
@@ -45239,7 +45239,7 @@
       </c>
       <c r="M921" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t>socioeconomic status category</t>
         </is>
       </c>
       <c r="R921" t="inlineStr">
@@ -45251,22 +45251,22 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>BCIO:015494</t>
+          <t>BCIO:015728</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>insured party role population statistic</t>
+          <t>proportion socioeconomic status category population statistic</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>A population statistic about insured party role.</t>
+          <t>A(n) socioeconomic status category population statistic that is the proportion of people that have a socioeconomic status category in the population.</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>population statistic</t>
+          <t>socioeconomic status category population statistic</t>
         </is>
       </c>
       <c r="K922" t="inlineStr">
@@ -45276,7 +45276,7 @@
       </c>
       <c r="M922" t="inlineStr">
         <is>
-          <t>insured party role</t>
+          <t>socioeconomic status category</t>
         </is>
       </c>
       <c r="R922" t="inlineStr">
@@ -45288,22 +45288,22 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>BCIO:015495</t>
+          <t>BCIO:015729</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>percentage insured party role population statistic</t>
+          <t>socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>A(n) insured party role population statistic that is the percentage of people that have a insured party role in the population.</t>
+          <t>A population statistic about socioeconomic status score.</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>insured party role population statistic</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="K923" t="inlineStr">
@@ -45313,7 +45313,7 @@
       </c>
       <c r="M923" t="inlineStr">
         <is>
-          <t>insured party role</t>
+          <t>socioeconomic status score</t>
         </is>
       </c>
       <c r="R923" t="inlineStr">
@@ -45325,22 +45325,22 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>BCIO:015496</t>
+          <t>BCIO:015730</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>proportion insured party role population statistic</t>
+          <t>mean socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>A(n) insured party role population statistic that is the proportion of people that have a insured party role in the population.</t>
+          <t>A(n) socioeconomic status score population statistic that is the mean value of socioeconomic status score in the population.</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>insured party role population statistic</t>
+          <t>socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="K924" t="inlineStr">
@@ -45350,7 +45350,7 @@
       </c>
       <c r="M924" t="inlineStr">
         <is>
-          <t>insured party role</t>
+          <t>socioeconomic status score</t>
         </is>
       </c>
       <c r="R924" t="inlineStr">
@@ -45362,22 +45362,22 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>BCIO:015526</t>
+          <t>BCIO:015731</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>masters student role population statistic</t>
+          <t>minimum socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>A population statistic about masters student role.</t>
+          <t>A(n) socioeconomic status score population statistic that is the minimum value of socioeconomic status score in the population.</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>higher education student role population statistic</t>
+          <t>socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="K925" t="inlineStr">
@@ -45387,7 +45387,7 @@
       </c>
       <c r="M925" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>socioeconomic status score</t>
         </is>
       </c>
       <c r="R925" t="inlineStr">
@@ -45399,22 +45399,22 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>BCIO:015527</t>
+          <t>BCIO:015732</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>percentage masters student role population statistic</t>
+          <t>maximum socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>A(n) masters student role population statistic that is the percentage of people that have a masters student role in the population.</t>
+          <t>A(n) socioeconomic status score population statistic that is the maximum value of socioeconomic status score in the population.</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>masters student role population statistic</t>
+          <t>socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="K926" t="inlineStr">
@@ -45424,7 +45424,7 @@
       </c>
       <c r="M926" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>socioeconomic status score</t>
         </is>
       </c>
       <c r="R926" t="inlineStr">
@@ -45436,22 +45436,22 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>BCIO:015528</t>
+          <t>BCIO:015733</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>proportion masters student role population statistic</t>
+          <t>median socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>A(n) masters student role population statistic that is the proportion of people that have a masters student role in the population.</t>
+          <t>A(n) socioeconomic status score population statistic that is the median value of socioeconomic status score in the population.</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>masters student role population statistic</t>
+          <t>socioeconomic status score population statistic</t>
         </is>
       </c>
       <c r="K927" t="inlineStr">
@@ -45461,7 +45461,7 @@
       </c>
       <c r="M927" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>socioeconomic status score</t>
         </is>
       </c>
       <c r="R927" t="inlineStr">
@@ -45473,22 +45473,22 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>BCIO:015613</t>
+          <t>BCIO:015799</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>past behaviour  population statistic</t>
+          <t>vocational training student or trainee role population statistic</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>A population statistic about past behaviour .</t>
+          <t>A population statistic about vocational training student or trainee role.</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>population statistic</t>
+          <t>student or trainee role population statistic</t>
         </is>
       </c>
       <c r="K928" t="inlineStr">
@@ -45498,7 +45498,7 @@
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t xml:space="preserve">past behaviour </t>
+          <t>vocational training student or trainee role</t>
         </is>
       </c>
       <c r="R928" t="inlineStr">
@@ -45510,22 +45510,22 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>BCIO:015614</t>
+          <t>BCIO:015800</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>mean past behaviour  population statistic</t>
+          <t>percentage vocational training student or trainee role population statistic</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>A(n) past behaviour  population statistic that is the mean value of past behaviour  in the population.</t>
+          <t>A(n) vocational training student or trainee role population statistic that is the percentage of people that have a vocational training student or trainee role in the population.</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>past behaviour  population statistic</t>
+          <t>vocational training student or trainee role population statistic</t>
         </is>
       </c>
       <c r="K929" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="M929" t="inlineStr">
         <is>
-          <t xml:space="preserve">past behaviour </t>
+          <t>vocational training student or trainee role</t>
         </is>
       </c>
       <c r="R929" t="inlineStr">
@@ -45547,22 +45547,22 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>BCIO:015615</t>
+          <t>BCIO:015801</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>minimum past behaviour  population statistic</t>
+          <t>proportion vocational training student or trainee role population statistic</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>A(n) past behaviour  population statistic that is the minimum value of past behaviour  in the population.</t>
+          <t>A(n) vocational training student or trainee role population statistic that is the proportion of people that have a vocational training student or trainee role in the population.</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>past behaviour  population statistic</t>
+          <t>vocational training student or trainee role population statistic</t>
         </is>
       </c>
       <c r="K930" t="inlineStr">
@@ -45572,898 +45572,10 @@
       </c>
       <c r="M930" t="inlineStr">
         <is>
-          <t xml:space="preserve">past behaviour </t>
+          <t>vocational training student or trainee role</t>
         </is>
       </c>
       <c r="R930" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr">
-        <is>
-          <t>BCIO:015616</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>maximum past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="C931" t="inlineStr">
-        <is>
-          <t>A(n) past behaviour  population statistic that is the maximum value of past behaviour  in the population.</t>
-        </is>
-      </c>
-      <c r="D931" t="inlineStr">
-        <is>
-          <t>past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="K931" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M931" t="inlineStr">
-        <is>
-          <t xml:space="preserve">past behaviour </t>
-        </is>
-      </c>
-      <c r="R931" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr">
-        <is>
-          <t>BCIO:015617</t>
-        </is>
-      </c>
-      <c r="B932" t="inlineStr">
-        <is>
-          <t>median past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="C932" t="inlineStr">
-        <is>
-          <t>A(n) past behaviour  population statistic that is the median value of past behaviour  in the population.</t>
-        </is>
-      </c>
-      <c r="D932" t="inlineStr">
-        <is>
-          <t>past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="K932" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M932" t="inlineStr">
-        <is>
-          <t xml:space="preserve">past behaviour </t>
-        </is>
-      </c>
-      <c r="R932" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr">
-        <is>
-          <t>BCIO:015618</t>
-        </is>
-      </c>
-      <c r="B933" t="inlineStr">
-        <is>
-          <t>percentage past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="C933" t="inlineStr">
-        <is>
-          <t>A(n) past behaviour  population statistic that is the percentage value of past behaviour  in the population.</t>
-        </is>
-      </c>
-      <c r="D933" t="inlineStr">
-        <is>
-          <t>past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="K933" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M933" t="inlineStr">
-        <is>
-          <t xml:space="preserve">past behaviour </t>
-        </is>
-      </c>
-      <c r="R933" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr">
-        <is>
-          <t>BCIO:015619</t>
-        </is>
-      </c>
-      <c r="B934" t="inlineStr">
-        <is>
-          <t>proportion past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="C934" t="inlineStr">
-        <is>
-          <t>A(n) past behaviour  population statistic that is the proportion of individuals having a past behaviour  in the population.</t>
-        </is>
-      </c>
-      <c r="D934" t="inlineStr">
-        <is>
-          <t>past behaviour  population statistic</t>
-        </is>
-      </c>
-      <c r="K934" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M934" t="inlineStr">
-        <is>
-          <t xml:space="preserve">past behaviour </t>
-        </is>
-      </c>
-      <c r="R934" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr">
-        <is>
-          <t>BCIO:015737</t>
-        </is>
-      </c>
-      <c r="B935" t="inlineStr">
-        <is>
-          <t>school student role population statistic</t>
-        </is>
-      </c>
-      <c r="C935" t="inlineStr">
-        <is>
-          <t>A population statistic about school student role.</t>
-        </is>
-      </c>
-      <c r="D935" t="inlineStr">
-        <is>
-          <t>student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K935" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M935" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
-      <c r="R935" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr">
-        <is>
-          <t>BCIO:015738</t>
-        </is>
-      </c>
-      <c r="B936" t="inlineStr">
-        <is>
-          <t>percentage school student role population statistic</t>
-        </is>
-      </c>
-      <c r="C936" t="inlineStr">
-        <is>
-          <t>A(n) school student role population statistic that is the percentage of people that have a school student role in the population.</t>
-        </is>
-      </c>
-      <c r="D936" t="inlineStr">
-        <is>
-          <t>school student role population statistic</t>
-        </is>
-      </c>
-      <c r="K936" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M936" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
-      <c r="R936" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr">
-        <is>
-          <t>BCIO:015739</t>
-        </is>
-      </c>
-      <c r="B937" t="inlineStr">
-        <is>
-          <t>proportion school student role population statistic</t>
-        </is>
-      </c>
-      <c r="C937" t="inlineStr">
-        <is>
-          <t>A(n) school student role population statistic that is the proportion of people that have a school student role in the population.</t>
-        </is>
-      </c>
-      <c r="D937" t="inlineStr">
-        <is>
-          <t>school student role population statistic</t>
-        </is>
-      </c>
-      <c r="K937" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M937" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
-      <c r="R937" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr">
-        <is>
-          <t>BCIO:015758</t>
-        </is>
-      </c>
-      <c r="B938" t="inlineStr">
-        <is>
-          <t>socioeconomic status category population statistic</t>
-        </is>
-      </c>
-      <c r="C938" t="inlineStr">
-        <is>
-          <t>A population statistic about socioeconomic status category.</t>
-        </is>
-      </c>
-      <c r="D938" t="inlineStr">
-        <is>
-          <t>population statistic</t>
-        </is>
-      </c>
-      <c r="K938" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M938" t="inlineStr">
-        <is>
-          <t>socioeconomic status category</t>
-        </is>
-      </c>
-      <c r="R938" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr">
-        <is>
-          <t>BCIO:015759</t>
-        </is>
-      </c>
-      <c r="B939" t="inlineStr">
-        <is>
-          <t>percentage socioeconomic status category population statistic</t>
-        </is>
-      </c>
-      <c r="C939" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status category population statistic that is the percentage of people that have a socioeconomic status category in the population.</t>
-        </is>
-      </c>
-      <c r="D939" t="inlineStr">
-        <is>
-          <t>socioeconomic status category population statistic</t>
-        </is>
-      </c>
-      <c r="K939" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M939" t="inlineStr">
-        <is>
-          <t>socioeconomic status category</t>
-        </is>
-      </c>
-      <c r="R939" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr">
-        <is>
-          <t>BCIO:015760</t>
-        </is>
-      </c>
-      <c r="B940" t="inlineStr">
-        <is>
-          <t>proportion socioeconomic status category population statistic</t>
-        </is>
-      </c>
-      <c r="C940" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status category population statistic that is the proportion of people that have a socioeconomic status category in the population.</t>
-        </is>
-      </c>
-      <c r="D940" t="inlineStr">
-        <is>
-          <t>socioeconomic status category population statistic</t>
-        </is>
-      </c>
-      <c r="K940" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M940" t="inlineStr">
-        <is>
-          <t>socioeconomic status category</t>
-        </is>
-      </c>
-      <c r="R940" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr">
-        <is>
-          <t>BCIO:015761</t>
-        </is>
-      </c>
-      <c r="B941" t="inlineStr">
-        <is>
-          <t>socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="C941" t="inlineStr">
-        <is>
-          <t>A population statistic about socioeconomic status score.</t>
-        </is>
-      </c>
-      <c r="D941" t="inlineStr">
-        <is>
-          <t>population statistic</t>
-        </is>
-      </c>
-      <c r="K941" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M941" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="R941" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="942">
-      <c r="A942" t="inlineStr">
-        <is>
-          <t>BCIO:015762</t>
-        </is>
-      </c>
-      <c r="B942" t="inlineStr">
-        <is>
-          <t>mean socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="C942" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status score population statistic that is the mean value of socioeconomic status score in the population.</t>
-        </is>
-      </c>
-      <c r="D942" t="inlineStr">
-        <is>
-          <t>socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="K942" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M942" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="R942" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="943">
-      <c r="A943" t="inlineStr">
-        <is>
-          <t>BCIO:015763</t>
-        </is>
-      </c>
-      <c r="B943" t="inlineStr">
-        <is>
-          <t>minimum socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="C943" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status score population statistic that is the minimum value of socioeconomic status score in the population.</t>
-        </is>
-      </c>
-      <c r="D943" t="inlineStr">
-        <is>
-          <t>socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="K943" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M943" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="R943" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="944">
-      <c r="A944" t="inlineStr">
-        <is>
-          <t>BCIO:015764</t>
-        </is>
-      </c>
-      <c r="B944" t="inlineStr">
-        <is>
-          <t>maximum socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="C944" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status score population statistic that is the maximum value of socioeconomic status score in the population.</t>
-        </is>
-      </c>
-      <c r="D944" t="inlineStr">
-        <is>
-          <t>socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="K944" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M944" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="R944" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="945">
-      <c r="A945" t="inlineStr">
-        <is>
-          <t>BCIO:015765</t>
-        </is>
-      </c>
-      <c r="B945" t="inlineStr">
-        <is>
-          <t>median socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="C945" t="inlineStr">
-        <is>
-          <t>A(n) socioeconomic status score population statistic that is the median value of socioeconomic status score in the population.</t>
-        </is>
-      </c>
-      <c r="D945" t="inlineStr">
-        <is>
-          <t>socioeconomic status score population statistic</t>
-        </is>
-      </c>
-      <c r="K945" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M945" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="R945" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="946">
-      <c r="A946" t="inlineStr">
-        <is>
-          <t>BCIO:015817</t>
-        </is>
-      </c>
-      <c r="B946" t="inlineStr">
-        <is>
-          <t>undergraduate student role population statistic</t>
-        </is>
-      </c>
-      <c r="C946" t="inlineStr">
-        <is>
-          <t>A population statistic about undergraduate student role.</t>
-        </is>
-      </c>
-      <c r="D946" t="inlineStr">
-        <is>
-          <t>higher education student role population statistic</t>
-        </is>
-      </c>
-      <c r="K946" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M946" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="R946" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="947">
-      <c r="A947" t="inlineStr">
-        <is>
-          <t>BCIO:015818</t>
-        </is>
-      </c>
-      <c r="B947" t="inlineStr">
-        <is>
-          <t>percentage undergraduate student role population statistic</t>
-        </is>
-      </c>
-      <c r="C947" t="inlineStr">
-        <is>
-          <t>A(n) undergraduate student role population statistic that is the percentage of people that have a undergraduate student role in the population.</t>
-        </is>
-      </c>
-      <c r="D947" t="inlineStr">
-        <is>
-          <t>undergraduate student role population statistic</t>
-        </is>
-      </c>
-      <c r="K947" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M947" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="R947" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="948">
-      <c r="A948" t="inlineStr">
-        <is>
-          <t>BCIO:015819</t>
-        </is>
-      </c>
-      <c r="B948" t="inlineStr">
-        <is>
-          <t>proportion undergraduate student role population statistic</t>
-        </is>
-      </c>
-      <c r="C948" t="inlineStr">
-        <is>
-          <t>A(n) undergraduate student role population statistic that is the proportion of people that have a undergraduate student role in the population.</t>
-        </is>
-      </c>
-      <c r="D948" t="inlineStr">
-        <is>
-          <t>undergraduate student role population statistic</t>
-        </is>
-      </c>
-      <c r="K948" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M948" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="R948" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="949">
-      <c r="A949" t="inlineStr">
-        <is>
-          <t>BCIO:015834</t>
-        </is>
-      </c>
-      <c r="B949" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C949" t="inlineStr">
-        <is>
-          <t>A population statistic about vocational training student or trainee role.</t>
-        </is>
-      </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K949" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M949" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R949" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="950">
-      <c r="A950" t="inlineStr">
-        <is>
-          <t>BCIO:015835</t>
-        </is>
-      </c>
-      <c r="B950" t="inlineStr">
-        <is>
-          <t>percentage vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C950" t="inlineStr">
-        <is>
-          <t>A(n) vocational training student or trainee role population statistic that is the percentage of people that have a vocational training student or trainee role in the population.</t>
-        </is>
-      </c>
-      <c r="D950" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K950" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M950" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R950" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="951">
-      <c r="A951" t="inlineStr">
-        <is>
-          <t>BCIO:015836</t>
-        </is>
-      </c>
-      <c r="B951" t="inlineStr">
-        <is>
-          <t>proportion vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C951" t="inlineStr">
-        <is>
-          <t>A(n) vocational training student or trainee role population statistic that is the proportion of people that have a vocational training student or trainee role in the population.</t>
-        </is>
-      </c>
-      <c r="D951" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K951" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M951" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R951" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="952">
-      <c r="A952" t="inlineStr">
-        <is>
-          <t>BCIO:015837</t>
-        </is>
-      </c>
-      <c r="B952" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C952" t="inlineStr">
-        <is>
-          <t>A population statistic about vocational training student or trainee role.</t>
-        </is>
-      </c>
-      <c r="D952" t="inlineStr">
-        <is>
-          <t>student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K952" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M952" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R952" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="953">
-      <c r="A953" t="inlineStr">
-        <is>
-          <t>BCIO:015838</t>
-        </is>
-      </c>
-      <c r="B953" t="inlineStr">
-        <is>
-          <t>percentage vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C953" t="inlineStr">
-        <is>
-          <t>A(n) vocational training student or trainee role population statistic that is the percentage of people that have a vocational training student or trainee role in the population.</t>
-        </is>
-      </c>
-      <c r="D953" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K953" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M953" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R953" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-    </row>
-    <row r="954">
-      <c r="A954" t="inlineStr">
-        <is>
-          <t>BCIO:015839</t>
-        </is>
-      </c>
-      <c r="B954" t="inlineStr">
-        <is>
-          <t>proportion vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="C954" t="inlineStr">
-        <is>
-          <t>A(n) vocational training student or trainee role population statistic that is the proportion of people that have a vocational training student or trainee role in the population.</t>
-        </is>
-      </c>
-      <c r="D954" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role population statistic</t>
-        </is>
-      </c>
-      <c r="K954" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="M954" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="R954" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -3258,12 +3258,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
+          <t>A personal attribute relating the bearer to an employment process.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>An attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
+          <t>A personal attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -5012,7 +5012,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -25117,7 +25117,7 @@
       <c r="Q520" t="inlineStr"/>
       <c r="R520" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S520" t="inlineStr"/>
@@ -25168,7 +25168,7 @@
       <c r="Q521" t="inlineStr"/>
       <c r="R521" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S521" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       <c r="Q522" t="inlineStr"/>
       <c r="R522" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S522" t="inlineStr"/>
@@ -25270,7 +25270,7 @@
       <c r="Q523" t="inlineStr"/>
       <c r="R523" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S523" t="inlineStr"/>
@@ -25321,7 +25321,7 @@
       <c r="Q524" t="inlineStr"/>
       <c r="R524" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S524" t="inlineStr"/>
@@ -25372,7 +25372,7 @@
       <c r="Q525" t="inlineStr"/>
       <c r="R525" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S525" t="inlineStr"/>
@@ -25423,7 +25423,7 @@
       <c r="Q526" t="inlineStr"/>
       <c r="R526" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S526" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -5423,7 +5423,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -26647,7 +26647,7 @@
       <c r="Q550" t="inlineStr"/>
       <c r="R550" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S550" t="inlineStr"/>
@@ -26698,7 +26698,7 @@
       <c r="Q551" t="inlineStr"/>
       <c r="R551" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S551" t="inlineStr"/>
@@ -26749,7 +26749,7 @@
       <c r="Q552" t="inlineStr"/>
       <c r="R552" t="inlineStr">
         <is>
-          <t>Discussed</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S552" t="inlineStr"/>

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -2425,12 +2425,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
+          <t>A personal role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
